--- a/Result/profitability/3687.xlsx
+++ b/Result/profitability/3687.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>10.14</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0275</v>
+        <v>1.9975</v>
       </c>
       <c r="N2" t="n">
-        <v>43.70875</v>
+        <v>43.76125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9075</v>
+        <v>1.87375</v>
       </c>
       <c r="N3" t="n">
-        <v>45.99125</v>
+        <v>45.9975</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8075</v>
+        <v>1.77375</v>
       </c>
       <c r="N4" t="n">
-        <v>46.92125</v>
+        <v>46.85875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.895</v>
+        <v>1.88625</v>
       </c>
       <c r="N5" t="n">
-        <v>49.50875</v>
+        <v>49.39125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.98125</v>
+        <v>1.5725</v>
       </c>
       <c r="N6" t="n">
-        <v>51.71375</v>
+        <v>51.67749999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6975</v>
+        <v>1.70875</v>
       </c>
       <c r="N7" t="n">
-        <v>53.82624999999999</v>
+        <v>53.86375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.05</v>
       </c>
       <c r="M8" t="n">
-        <v>1.80375</v>
+        <v>1.80125</v>
       </c>
       <c r="N8" t="n">
-        <v>55.825</v>
+        <v>55.735</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3687</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>504</v>
+      </c>
+      <c r="D71" t="n">
+        <v>303</v>
+      </c>
+      <c r="E71" t="n">
+        <v>202</v>
+      </c>
+      <c r="F71" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="G71" t="n">
+        <v>85</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>16.90%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>17</v>
+      </c>
+      <c r="J71" t="n">
+        <v>103</v>
+      </c>
+      <c r="K71" t="n">
+        <v>9</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.79625</v>
+      </c>
+      <c r="N71" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X71" t="n">
+        <v>-0.06451612903225812</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.01768607221812823</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-0.1944444444444444</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-0.9399999999999977</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-0.02296603957977028</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
